--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$113</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:27:43+00:00</t>
+    <t>2026-01-30T14:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,10 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">**Beschreibung:** Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
-- 1..1 List: Liste der Medikationsplaneinträge und deren Änderungsstatus
-- 0..* MedicationRequests: Medikationsplaneinträge 
-</t>
+    <t>**Beschreibung:** Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
+- 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus) 
+- 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -611,7 +613,7 @@
     <t>Bundle.entry.fullUrl</t>
   </si>
   <si>
-    <t>Eindeutige URL für den Eintrag im Bundle. Verwendung prüfen.</t>
+    <t xml:space="preserve">Eindeutige URL für den Eintrag im Bundle. </t>
   </si>
   <si>
     <t>The Absolute URL for the resource.  The fullUrl SHALL NOT disagree with the id in the resource - i.e. if the fullUrl is not a urn:uuid, the URL shall be version-independent URL consistent with the Resource.id. The fullUrl is a version independent reference to the resource. The fullUrl element SHALL have a value except that: 
@@ -1229,6 +1231,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1576,7 +1593,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1688,7 +1705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -1802,7 +1819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -1914,7 +1931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -2028,7 +2045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -2161,7 +2178,7 @@
         <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -2275,7 +2292,7 @@
         <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
@@ -2389,7 +2406,7 @@
         <v>87</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>21</v>
@@ -2484,7 +2501,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
@@ -2598,7 +2615,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2614,7 +2631,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2712,7 +2729,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>149</v>
       </c>
@@ -2824,7 +2841,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>155</v>
       </c>
@@ -2938,7 +2955,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>163</v>
       </c>
@@ -3054,7 +3071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>169</v>
       </c>
@@ -3166,7 +3183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>172</v>
       </c>
@@ -3278,7 +3295,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>175</v>
       </c>
@@ -3388,7 +3405,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>181</v>
       </c>
@@ -3500,7 +3517,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>182</v>
       </c>
@@ -3614,7 +3631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>183</v>
       </c>
@@ -3730,7 +3747,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>184</v>
       </c>
@@ -3842,7 +3859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>187</v>
       </c>
@@ -3858,7 +3875,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -3956,7 +3973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>191</v>
       </c>
@@ -4068,7 +4085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>195</v>
       </c>
@@ -4180,7 +4197,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>199</v>
       </c>
@@ -4292,7 +4309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>200</v>
       </c>
@@ -4406,7 +4423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>201</v>
       </c>
@@ -4522,7 +4539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>202</v>
       </c>
@@ -4636,7 +4653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>208</v>
       </c>
@@ -4750,7 +4767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>213</v>
       </c>
@@ -4862,7 +4879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>217</v>
       </c>
@@ -4974,7 +4991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>218</v>
       </c>
@@ -5088,7 +5105,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>219</v>
       </c>
@@ -5204,7 +5221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>220</v>
       </c>
@@ -5316,7 +5333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>225</v>
       </c>
@@ -5430,7 +5447,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>229</v>
       </c>
@@ -5542,7 +5559,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>232</v>
       </c>
@@ -5654,7 +5671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>234</v>
       </c>
@@ -5766,7 +5783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>237</v>
       </c>
@@ -5878,7 +5895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>240</v>
       </c>
@@ -5990,7 +6007,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>244</v>
       </c>
@@ -6102,7 +6119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>245</v>
       </c>
@@ -6216,7 +6233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>246</v>
       </c>
@@ -6332,7 +6349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>247</v>
       </c>
@@ -6444,7 +6461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>250</v>
       </c>
@@ -6556,7 +6573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>253</v>
       </c>
@@ -6670,7 +6687,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>257</v>
       </c>
@@ -6784,7 +6801,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>261</v>
       </c>
@@ -6898,7 +6915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>265</v>
       </c>
@@ -7012,7 +7029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>267</v>
       </c>
@@ -7124,7 +7141,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>268</v>
       </c>
@@ -7238,7 +7255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>269</v>
       </c>
@@ -7354,7 +7371,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>270</v>
       </c>
@@ -7466,7 +7483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>271</v>
       </c>
@@ -7482,7 +7499,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7580,7 +7597,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>272</v>
       </c>
@@ -7692,7 +7709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>278</v>
       </c>
@@ -7804,7 +7821,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>279</v>
       </c>
@@ -7916,7 +7933,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>280</v>
       </c>
@@ -8030,7 +8047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>281</v>
       </c>
@@ -8146,7 +8163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>282</v>
       </c>
@@ -8260,7 +8277,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>283</v>
       </c>
@@ -8374,7 +8391,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>284</v>
       </c>
@@ -8486,7 +8503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>285</v>
       </c>
@@ -8598,7 +8615,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>286</v>
       </c>
@@ -8712,7 +8729,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>287</v>
       </c>
@@ -8828,7 +8845,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>288</v>
       </c>
@@ -8940,7 +8957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>289</v>
       </c>
@@ -9054,7 +9071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>290</v>
       </c>
@@ -9166,7 +9183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>291</v>
       </c>
@@ -9278,7 +9295,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>292</v>
       </c>
@@ -9390,7 +9407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>293</v>
       </c>
@@ -9502,7 +9519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>294</v>
       </c>
@@ -9614,7 +9631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>295</v>
       </c>
@@ -9726,7 +9743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>296</v>
       </c>
@@ -9840,7 +9857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>297</v>
       </c>
@@ -9956,7 +9973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>298</v>
       </c>
@@ -10068,7 +10085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>299</v>
       </c>
@@ -10180,7 +10197,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>300</v>
       </c>
@@ -10294,7 +10311,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>301</v>
       </c>
@@ -10408,7 +10425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>302</v>
       </c>
@@ -10522,7 +10539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>303</v>
       </c>
@@ -10636,7 +10653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>305</v>
       </c>
@@ -10748,7 +10765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>306</v>
       </c>
@@ -10862,7 +10879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>307</v>
       </c>
@@ -10978,7 +10995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>308</v>
       </c>
@@ -11090,7 +11107,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
         <v>309</v>
       </c>
@@ -11106,7 +11123,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>21</v>
@@ -11204,7 +11221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
         <v>310</v>
       </c>
@@ -11316,7 +11333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
         <v>316</v>
       </c>
@@ -11428,7 +11445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
         <v>317</v>
       </c>
@@ -11540,7 +11557,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
         <v>318</v>
       </c>
@@ -11654,7 +11671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
         <v>319</v>
       </c>
@@ -11770,7 +11787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
         <v>320</v>
       </c>
@@ -11884,7 +11901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>321</v>
       </c>
@@ -11998,7 +12015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
         <v>322</v>
       </c>
@@ -12110,7 +12127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
         <v>323</v>
       </c>
@@ -12222,7 +12239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
         <v>324</v>
       </c>
@@ -12336,7 +12353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
         <v>325</v>
       </c>
@@ -12452,7 +12469,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
         <v>326</v>
       </c>
@@ -12564,7 +12581,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
         <v>327</v>
       </c>
@@ -12678,7 +12695,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
         <v>328</v>
       </c>
@@ -12790,7 +12807,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
         <v>329</v>
       </c>
@@ -12902,7 +12919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
         <v>330</v>
       </c>
@@ -13014,7 +13031,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
         <v>331</v>
       </c>
@@ -13126,7 +13143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
         <v>332</v>
       </c>
@@ -13238,7 +13255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
         <v>333</v>
       </c>
@@ -13350,7 +13367,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
         <v>334</v>
       </c>
@@ -13464,7 +13481,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
         <v>335</v>
       </c>
@@ -13580,7 +13597,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
         <v>336</v>
       </c>
@@ -13692,7 +13709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
         <v>337</v>
       </c>
@@ -13804,7 +13821,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
         <v>338</v>
       </c>
@@ -13918,7 +13935,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
         <v>339</v>
       </c>
@@ -14032,7 +14049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
         <v>340</v>
       </c>
@@ -14146,7 +14163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
         <v>341</v>
       </c>
@@ -14263,6 +14280,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN113">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI112">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:55:57+00:00</t>
+    <t>2026-02-09T17:27:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T17:27:03+00:00</t>
+    <t>2026-02-10T17:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T17:53:58+00:00</t>
+    <t>2026-02-12T16:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T16:23:56+00:00</t>
+    <t>2026-02-16T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:10:16+00:00</t>
+    <t>2026-02-16T15:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T15:59:40+00:00</t>
+    <t>2026-02-17T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T17:15:57+00:00</t>
+    <t>2026-02-20T10:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
+    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
 - 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus) 
 - 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AtEmedBundleMedikationsplanTx</t>
+    <t>AtEmedBundleTxMedikationsplan</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="346">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1000,9 +1000,6 @@
   <si>
     <t xml:space="preserve">MedicationRequest {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-mr-planeintrag}
 </t>
-  </si>
-  <si>
-    <t>Ordering of medication for patient or group</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>
@@ -11252,10 +11249,10 @@
         <v>312</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11324,7 +11321,7 @@
         <v>21</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>21</v>
@@ -11335,7 +11332,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>195</v>
@@ -11447,7 +11444,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>199</v>
@@ -11559,7 +11556,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>200</v>
@@ -11673,7 +11670,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>201</v>
@@ -11789,7 +11786,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>202</v>
@@ -11903,7 +11900,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>208</v>
@@ -12017,7 +12014,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>213</v>
@@ -12129,7 +12126,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>217</v>
@@ -12241,7 +12238,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>218</v>
@@ -12355,7 +12352,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>219</v>
@@ -12471,7 +12468,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>220</v>
@@ -12583,7 +12580,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>225</v>
@@ -12697,7 +12694,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>229</v>
@@ -12809,7 +12806,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>232</v>
@@ -12921,7 +12918,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>234</v>
@@ -13033,7 +13030,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>237</v>
@@ -13145,7 +13142,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>240</v>
@@ -13257,7 +13254,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>244</v>
@@ -13369,7 +13366,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>245</v>
@@ -13483,7 +13480,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>246</v>
@@ -13599,7 +13596,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>247</v>
@@ -13711,7 +13708,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>250</v>
@@ -13823,7 +13820,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>253</v>
@@ -13937,7 +13934,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>257</v>
@@ -14051,7 +14048,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>261</v>
@@ -14165,10 +14162,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14191,19 +14188,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -14252,7 +14249,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
   </si>
   <si>
     <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
-- 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus) 
+- 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus 
 - 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
   </si>
   <si>
@@ -428,7 +428,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitpunkt der Erstellung des Bundles. Verwendung prüfen.</t>
+    <t>Zeitpunkt der Erstellung des Bundles.</t>
   </si>
   <si>
     <t>The date/time that the bundle was assembled - i.e. when the resources were placed in the bundle.</t>
@@ -477,7 +477,7 @@
 </t>
   </si>
   <si>
-    <t>Verweise auf weiterführende Informationen zum Bundle. Verwendung prüfen.</t>
+    <t>Verweise auf weiterführende Informationen zum Bundle.</t>
   </si>
   <si>
     <t>A series of links that provide context to this bundle.</t>
@@ -604,7 +604,7 @@
     <t>Bundle.entry.link</t>
   </si>
   <si>
-    <t>Verweise auf weiterführende Informationen zu diesem Entry. Verwendung prüfen.</t>
+    <t>Verweise auf weiterführende Informationen zu diesem Entry.</t>
   </si>
   <si>
     <t>A series of links that provide context to this entry.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-bundle-tx-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
